--- a/数据表/Datas/EnemyConfig_敌人配置.xlsx
+++ b/数据表/Datas/EnemyConfig_敌人配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16060"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -65,6 +65,9 @@
     <t>dropTableId</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>(list#sep=,),int</t>
   </si>
   <si>
+    <t>string#ref=TbSpriteConfig</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -90,6 +96,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>敌人</t>
     </r>
     <r>
@@ -107,6 +119,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>HP</t>
     </r>
     <r>
@@ -121,6 +139,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>MP</t>
     </r>
     <r>
@@ -144,6 +168,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>威胁等级</t>
     </r>
     <r>
@@ -158,6 +188,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>AI</t>
     </r>
     <r>
@@ -172,6 +208,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>可随机选择的行动</t>
     </r>
     <r>
@@ -186,6 +228,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>独立掉落表</t>
     </r>
     <r>
@@ -200,6 +248,23 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图标资源配置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>敌人</t>
     </r>
     <r>
@@ -220,6 +285,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>敌人</t>
     </r>
     <r>
@@ -234,6 +305,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>敌人</t>
     </r>
     <r>
@@ -465,7 +542,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,18 +594,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -866,7 +931,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -932,85 +997,85 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1528,8 +1593,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="6"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="8" width="10" style="2" customWidth="1"/>
@@ -1537,10 +1602,11 @@
     <col min="10" max="10" width="13" style="2" customWidth="1"/>
     <col min="11" max="11" width="19" style="2" customWidth="1"/>
     <col min="12" max="12" width="13" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="13" max="13" width="33.2058823529412" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:12">
+    <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1577,128 +1643,138 @@
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:12">
+    <row r="2" customHeight="1" spans="1:13">
       <c r="A2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:12">
+    <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="M3" s="8"/>
     </row>
-    <row r="4" customHeight="1" spans="1:12">
+    <row r="4" customHeight="1" spans="1:13">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:12">
+    <row r="5" customHeight="1" spans="1:13">
       <c r="A5" s="12"/>
       <c r="B5" s="13">
         <v>3001</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" s="13">
         <v>50</v>
@@ -1719,22 +1795,25 @@
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L5" s="13">
         <v>1</v>
       </c>
+      <c r="M5" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" customHeight="1" spans="1:12">
+    <row r="6" customHeight="1" spans="1:13">
       <c r="A6" s="12"/>
       <c r="B6" s="13">
         <v>3002</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" s="13">
         <v>80</v>
@@ -1755,22 +1834,25 @@
         <v>2</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L6" s="13">
         <v>2</v>
       </c>
+      <c r="M6" s="14" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="1:12">
+    <row r="7" customHeight="1" spans="1:13">
       <c r="A7" s="12"/>
       <c r="B7" s="13">
         <v>3003</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" s="13">
         <v>60</v>
@@ -1791,14 +1873,20 @@
         <v>3</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L7" s="13">
         <v>3</v>
       </c>
+      <c r="M7" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
+      <c r="M8" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/EnemyConfig_敌人配置.xlsx
+++ b/数据表/Datas/EnemyConfig_敌人配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16060"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -278,7 +278,7 @@
     </r>
   </si>
   <si>
-    <t>Random</t>
+    <t>随机行动</t>
   </si>
   <si>
     <t>201</t>
@@ -337,7 +337,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -388,6 +388,12 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -934,153 +940,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1120,6 +1126,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1794,7 +1803,7 @@
       <c r="I5" s="13">
         <v>1</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="15" t="s">
         <v>35</v>
       </c>
       <c r="K5" s="13" t="s">
@@ -1833,7 +1842,7 @@
       <c r="I6" s="13">
         <v>2</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="K6" s="13" t="s">
@@ -1872,7 +1881,7 @@
       <c r="I7" s="13">
         <v>3</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="15" t="s">
         <v>35</v>
       </c>
       <c r="K7" s="13" t="s">

--- a/数据表/Datas/EnemyConfig_敌人配置.xlsx
+++ b/数据表/Datas/EnemyConfig_敌人配置.xlsx
@@ -1602,8 +1602,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="7"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="8" width="10" style="2" customWidth="1"/>
@@ -1818,84 +1818,114 @@
     </row>
     <row r="6" customHeight="1" spans="1:13">
       <c r="A6" s="12"/>
-      <c r="B6" s="13">
-        <v>3002</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="13">
-        <v>80</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
-        <v>12</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
-        <v>10</v>
-      </c>
-      <c r="I6" s="13">
-        <v>2</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="13">
-        <v>2</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>37</v>
-      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="14"/>
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="A7" s="12"/>
       <c r="B7" s="13">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="13">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E7" s="13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F7" s="13">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" s="13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H7" s="13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I7" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="15" t="s">
         <v>35</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L7" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
-      <c r="M8" s="13"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="14"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13">
+        <v>3003</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="13">
+        <v>60</v>
+      </c>
+      <c r="E9" s="13">
+        <v>30</v>
+      </c>
+      <c r="F9" s="13">
+        <v>6</v>
+      </c>
+      <c r="G9" s="13">
+        <v>12</v>
+      </c>
+      <c r="H9" s="13">
+        <v>12</v>
+      </c>
+      <c r="I9" s="13">
+        <v>3</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="13">
+        <v>3</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
+      <c r="M10" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/EnemyConfig_敌人配置.xlsx
+++ b/数据表/Datas/EnemyConfig_敌人配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -115,9 +115,87 @@
     </r>
   </si>
   <si>
-    <t>原型名</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原型名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>HP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>威胁等级</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -125,7 +203,12 @@
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
-      <t>HP</t>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI</t>
     </r>
     <r>
       <rPr>
@@ -134,10 +217,19 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>上限</t>
-    </r>
-  </si>
-  <si>
+      <t>行为</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可随机选择的行动</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -145,8 +237,10 @@
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
-      <t>MP</t>
-    </r>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -154,17 +248,17 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>上限</t>
-    </r>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>魔力</t>
-  </si>
-  <si>
-    <t>速度</t>
+      <t>独立掉落表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ID</t>
+    </r>
   </si>
   <si>
     <r>
@@ -174,86 +268,6 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>威胁等级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>行为</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可随机选择的行动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>独立掉落表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
       <t>图标资源配置</t>
     </r>
   </si>
@@ -278,12 +292,6 @@
     </r>
   </si>
   <si>
-    <t>随机行动</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -291,6 +299,20 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
+      <t>随机行动</t>
+    </r>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>敌人</t>
     </r>
     <r>
@@ -325,6 +347,168 @@
   </si>
   <si>
     <t>201,202</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -374,26 +558,8 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -546,6 +712,23 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -940,19 +1123,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -961,132 +1156,120 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1113,22 +1296,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1602,7 +1776,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1746,10 +1920,10 @@
       <c r="C4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="10" t="s">
@@ -1764,7 +1938,7 @@
       <c r="I4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K4" s="10" t="s">
@@ -1773,159 +1947,507 @@
       <c r="L4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:13">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12">
         <v>3001</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>50</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>0</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>8</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>0</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>8</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>1</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <v>1</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:13">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" customHeight="1" spans="1:13">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12">
         <v>3002</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>80</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>0</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>12</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>0</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>10</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <v>2</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="12">
         <v>2</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="14"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
     </row>
     <row r="9" customHeight="1" spans="1:13">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12">
         <v>3003</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>60</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>30</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>6</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>12</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>12</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <v>3</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="12">
         <v>3</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:13">
-      <c r="M10" s="13"/>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
+      <c r="B11" s="12">
+        <v>3004</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="12">
+        <v>80</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>12</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>10</v>
+      </c>
+      <c r="I11" s="12">
+        <v>2</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="12">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="B13" s="12">
+        <v>3005</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="12">
+        <v>80</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
+        <v>12</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>10</v>
+      </c>
+      <c r="I13" s="12">
+        <v>2</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="12">
+        <v>2</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
+      <c r="B15" s="12">
+        <v>3006</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="12">
+        <v>80</v>
+      </c>
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>12</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12">
+        <v>10</v>
+      </c>
+      <c r="I15" s="12">
+        <v>2</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="12">
+        <v>2</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:13">
+      <c r="B17" s="12">
+        <v>3007</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="12">
+        <v>80</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>12</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>10</v>
+      </c>
+      <c r="I17" s="12">
+        <v>2</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="12">
+        <v>2</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:13">
+      <c r="B18" s="12"/>
+    </row>
+    <row r="19" customHeight="1" spans="2:13">
+      <c r="B19" s="12">
+        <v>3008</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="12">
+        <v>80</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12">
+        <v>12</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12">
+        <v>10</v>
+      </c>
+      <c r="I19" s="12">
+        <v>2</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="12">
+        <v>2</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:13">
+      <c r="B21" s="12">
+        <v>3009</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="12">
+        <v>80</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12">
+        <v>12</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12">
+        <v>10</v>
+      </c>
+      <c r="I21" s="12">
+        <v>2</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="12">
+        <v>2</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:13">
+      <c r="B23" s="12">
+        <v>3010</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="12">
+        <v>80</v>
+      </c>
+      <c r="E23" s="12">
+        <v>0</v>
+      </c>
+      <c r="F23" s="12">
+        <v>12</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12">
+        <v>10</v>
+      </c>
+      <c r="I23" s="12">
+        <v>2</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="12">
+        <v>2</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:13">
+      <c r="B25" s="12">
+        <v>3011</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="12">
+        <v>80</v>
+      </c>
+      <c r="E25" s="12">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12">
+        <v>12</v>
+      </c>
+      <c r="G25" s="12">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12">
+        <v>10</v>
+      </c>
+      <c r="I25" s="12">
+        <v>2</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="12">
+        <v>2</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:13">
+      <c r="B26" s="12"/>
+    </row>
+    <row r="27" customHeight="1" spans="2:13">
+      <c r="B27" s="12">
+        <v>3012</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="12">
+        <v>80</v>
+      </c>
+      <c r="E27" s="12">
+        <v>0</v>
+      </c>
+      <c r="F27" s="12">
+        <v>12</v>
+      </c>
+      <c r="G27" s="12">
+        <v>0</v>
+      </c>
+      <c r="H27" s="12">
+        <v>10</v>
+      </c>
+      <c r="I27" s="12">
+        <v>2</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" s="12">
+        <v>2</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
